--- a/03-Communication-and-Teamwork/Logbooks/Version-Control/Logbook - Kylie Afable v1.xlsx
+++ b/03-Communication-and-Teamwork/Logbooks/Version-Control/Logbook - Kylie Afable v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autuni-my.sharepoint.com/personal/cgr2690_autuni_ac_nz/Documents/Data/COMP703/Linux Networking/03-Communication-and-Teamwork/Logbooks/Version-Control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="280" documentId="13_ncr:1_{D484A641-6A78-43A6-B3E2-B28266551B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D055E2B-1F12-4320-9D20-052B277743C2}"/>
+  <xr:revisionPtr revIDLastSave="281" documentId="13_ncr:1_{D484A641-6A78-43A6-B3E2-B28266551B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD11591D-95A7-468C-8FBD-6FBDF12E836F}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>Catch up on Meeting</t>
   </si>
   <si>
-    <t>Was not able to attend meeting/reviewed meeting minutes/worked on mid progress report</t>
-  </si>
-  <si>
     <t xml:space="preserve">Project update and review of proposal </t>
   </si>
   <si>
@@ -276,6 +273,9 @@
   </si>
   <si>
     <t>Caught up on meeting/worked on proof read for our mid-term proposal</t>
+  </si>
+  <si>
+    <t>Was not able to attend meeting – had to review notes written during the meeting</t>
   </si>
 </sst>
 </file>
@@ -768,7 +768,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -789,7 +789,7 @@
         <v>3.0000000000000013</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>9</v>
@@ -837,10 +837,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,7 +903,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -927,7 +927,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -972,10 +972,10 @@
         <v>1.0000000000000018</v>
       </c>
       <c r="F12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1020,10 +1020,10 @@
         <v>2.0000000000000009</v>
       </c>
       <c r="F14" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F18" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1131,10 +1131,10 @@
         <v>2.4666666666666686</v>
       </c>
       <c r="F19" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1204,7 +1204,7 @@
         <v>16</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1307,10 +1307,10 @@
         <v>3.666666666666667</v>
       </c>
       <c r="F27" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="20" t="s">
         <v>76</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1701,7 +1701,7 @@
         <v>2.0000000000000009</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G45" s="20"/>
     </row>
@@ -1762,7 +1762,7 @@
         <v>43</v>
       </c>
       <c r="G48" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -1786,7 +1786,7 @@
         <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -1810,7 +1810,7 @@
         <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -1831,10 +1831,10 @@
         <v>1.0000000000000018</v>
       </c>
       <c r="F51" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" t="s">
         <v>47</v>
-      </c>
-      <c r="G51" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -1855,10 +1855,10 @@
         <v>2.0000000000000009</v>
       </c>
       <c r="F52" t="s">
+        <v>48</v>
+      </c>
+      <c r="G52" t="s">
         <v>49</v>
-      </c>
-      <c r="G52" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -1879,10 +1879,10 @@
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I53" s="1"/>
     </row>
@@ -1907,12 +1907,12 @@
         <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -1940,10 +1940,10 @@
         <v>3</v>
       </c>
       <c r="F57" t="s">
+        <v>53</v>
+      </c>
+      <c r="G57" t="s">
         <v>54</v>
-      </c>
-      <c r="G57" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -1988,7 +1988,7 @@
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2021,7 +2021,7 @@
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2042,7 +2042,7 @@
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2066,7 +2066,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2087,10 +2087,10 @@
         <v>0.99999999999999911</v>
       </c>
       <c r="F65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">

--- a/03-Communication-and-Teamwork/Logbooks/Version-Control/Logbook - Kylie Afable v1.xlsx
+++ b/03-Communication-and-Teamwork/Logbooks/Version-Control/Logbook - Kylie Afable v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autuni-my.sharepoint.com/personal/cgr2690_autuni_ac_nz/Documents/Data/COMP703/Linux Networking/03-Communication-and-Teamwork/Logbooks/Version-Control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="281" documentId="13_ncr:1_{D484A641-6A78-43A6-B3E2-B28266551B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD11591D-95A7-468C-8FBD-6FBDF12E836F}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="13_ncr:1_{D484A641-6A78-43A6-B3E2-B28266551B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F347DAEA-5776-463C-9292-F2C8C5CA7135}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>Date</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>Catch up on Meeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project update and review of proposal </t>
   </si>
   <si>
     <t>Discussion of status report</t>
@@ -768,7 +765,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -789,7 +786,7 @@
         <v>3.0000000000000013</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>9</v>
@@ -837,10 +834,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,7 +900,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -927,7 +924,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -972,10 +969,10 @@
         <v>1.0000000000000018</v>
       </c>
       <c r="F12" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>65</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1020,10 +1017,10 @@
         <v>2.0000000000000009</v>
       </c>
       <c r="F14" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1104,10 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="F18" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>70</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1131,10 +1128,10 @@
         <v>2.4666666666666686</v>
       </c>
       <c r="F19" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>72</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1204,7 +1201,7 @@
         <v>16</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1307,10 +1304,10 @@
         <v>3.666666666666667</v>
       </c>
       <c r="F27" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1701,7 +1698,7 @@
         <v>2.0000000000000009</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G45" s="20"/>
     </row>
@@ -1762,28 +1759,28 @@
         <v>43</v>
       </c>
       <c r="G48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>45804</v>
+        <v>45805</v>
       </c>
       <c r="B49">
         <v>9</v>
       </c>
       <c r="C49" s="3">
-        <v>0.54166666666666663</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="D49" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
       <c r="E49" s="1">
-        <f t="shared" si="3"/>
-        <v>1.0000000000000018</v>
+        <f>((D49-C49)*24)</f>
+        <v>1.5</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
         <v>44</v>
@@ -1797,44 +1794,44 @@
         <v>9</v>
       </c>
       <c r="C50" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="D50" s="3">
-        <v>0.85416666666666663</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="E50" s="1">
-        <f t="shared" si="3"/>
-        <v>1.5</v>
+        <f>((D50-C50)*24)</f>
+        <v>1.0000000000000018</v>
       </c>
       <c r="F50" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>45805</v>
+        <v>45806</v>
       </c>
       <c r="B51">
         <v>9</v>
       </c>
       <c r="C51" s="3">
-        <v>0.91666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D51" s="3">
-        <v>0.95833333333333337</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E51" s="1">
-        <f t="shared" si="3"/>
-        <v>1.0000000000000018</v>
+        <f>((D51-C51)*24)</f>
+        <v>2.0000000000000009</v>
       </c>
       <c r="F51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -1845,81 +1842,57 @@
         <v>9</v>
       </c>
       <c r="C52" s="3">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D52" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="E52" s="1">
         <f>((D52-C52)*24)</f>
-        <v>2.0000000000000009</v>
+        <v>3</v>
       </c>
       <c r="F52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G52" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>45806</v>
+        <v>45809</v>
       </c>
       <c r="B53">
         <v>9</v>
       </c>
       <c r="C53" s="3">
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D53" s="3">
-        <v>0.875</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="E53" s="1">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f>((D53-C53)*24)</f>
+        <v>2.5000000000000018</v>
       </c>
       <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" t="s">
         <v>50</v>
       </c>
-      <c r="G53" t="s">
-        <v>78</v>
-      </c>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>45809</v>
-      </c>
-      <c r="B54">
-        <v>9</v>
-      </c>
-      <c r="C54" s="3">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D54" s="3">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="E54" s="1">
-        <f>((D54-C54)*24)</f>
-        <v>2.5000000000000018</v>
-      </c>
-      <c r="F54" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="A54" s="9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="8">
-        <f>SUM(E48:E54)</f>
-        <v>13.000000000000007</v>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="8">
+        <f>SUM(E48:E53)</f>
+        <v>12.000000000000005</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -1940,10 +1913,10 @@
         <v>3</v>
       </c>
       <c r="F57" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57" t="s">
         <v>53</v>
-      </c>
-      <c r="G57" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -1988,7 +1961,7 @@
         <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2021,7 +1994,7 @@
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2042,7 +2015,7 @@
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2066,7 +2039,7 @@
         <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2087,10 +2060,10 @@
         <v>0.99999999999999911</v>
       </c>
       <c r="F65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -2110,8 +2083,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B48:B49 B44 B42 B40 B75 B86:B100 B46 B28:B29 B20:B26" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B48 B44 B42 B40 B75 B86:B100 B46 B28:B29 B20:B26" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1,2,3,4,5,6,7,8,9,10,11,12,13"</formula1>
     </dataValidation>
   </dataValidations>
